--- a/DTR/2026/APR16-30/AscendionNew_35311__John_2026-04-16-2026-04-30.xlsx
+++ b/DTR/2026/APR16-30/AscendionNew_35311__John_2026-04-16-2026-04-30.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="120">
   <si>
     <t xml:space="preserve">Client Name</t>
   </si>
@@ -390,7 +390,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="16">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
@@ -403,10 +403,9 @@
     <numFmt numFmtId="173" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="174" formatCode="m/d/yyyy\ h:mm"/>
     <numFmt numFmtId="175" formatCode="h:mm;@"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="178" formatCode="h:mm\ dd\-mmm\-yy"/>
-    <numFmt numFmtId="179" formatCode="h:mm\ mm/dd/yy"/>
+    <numFmt numFmtId="176" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="177" formatCode="h:mm\ dd\-mmm\-yy"/>
+    <numFmt numFmtId="178" formatCode="h:mm\ mm/dd/yy"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -733,24 +732,24 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="115">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -758,31 +757,31 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -790,39 +789,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -834,7 +833,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -842,7 +841,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -850,35 +849,35 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -886,19 +885,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -906,103 +905,103 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1010,19 +1009,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1030,19 +1029,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1054,7 +1053,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1066,7 +1065,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1078,7 +1077,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1090,19 +1089,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1110,10 +1109,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
@@ -1130,19 +1125,19 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1162,27 +1157,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1190,11 +1185,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1212,54 +1207,7 @@
     <cellStyle name="Normal 2 2" xfId="23"/>
     <cellStyle name="Normal 3" xfId="24"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9C0006"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB3A2C7"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC3D69B"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2462,7 +2410,9 @@
       <c r="K14" s="79"/>
       <c r="L14" s="84"/>
       <c r="M14" s="79"/>
-      <c r="N14" s="79"/>
+      <c r="N14" s="79" t="s">
+        <v>2</v>
+      </c>
       <c r="O14" s="85"/>
       <c r="P14" s="85"/>
       <c r="Q14" s="86" t="s">
@@ -3371,7 +3321,7 @@
       <c r="N16" s="79"/>
       <c r="O16" s="85"/>
       <c r="P16" s="85"/>
-      <c r="Q16" s="94"/>
+      <c r="Q16" s="86"/>
       <c r="R16" s="87" t="n">
         <f aca="false">IF(AND(C16="Normal",I16&gt;0),(8-S16),0)-IF(AND(C16="Normal",OR(C17="Special Holiday",C17="Working - Legal Holiday on RD",C17="Working - Special Holiday on RD",C17="Legal Holiday",C17="Legal Holiday on RD",C17="Special Holiday on RD")),BN16,0)+IF(AND(OR(C16="Normal",C16="Leave",C16="Rest Day"),OR(C15="Special Holiday",C15="Working - Legal Holiday on RD",C15="Working - Special Holiday on RD",C15="Legal Holiday")),BN15,0)</f>
         <v>0</v>
@@ -3823,7 +3773,7 @@
       <c r="N17" s="79"/>
       <c r="O17" s="85"/>
       <c r="P17" s="85"/>
-      <c r="Q17" s="94"/>
+      <c r="Q17" s="86"/>
       <c r="R17" s="87" t="n">
         <f aca="false">IF(AND(C17="Normal",I17&gt;0),(8-S17),0)-IF(AND(C17="Normal",OR(C18="Special Holiday",C18="Working - Legal Holiday on RD",C18="Working - Special Holiday on RD",C18="Legal Holiday",C18="Legal Holiday on RD",C18="Special Holiday on RD")),BN17,0)+IF(AND(OR(C17="Normal",C17="Leave",C17="Rest Day"),OR(C16="Special Holiday",C16="Working - Legal Holiday on RD",C16="Working - Special Holiday on RD",C16="Legal Holiday")),BN16,0)</f>
         <v>0</v>
@@ -4279,12 +4229,14 @@
         <v>0</v>
       </c>
       <c r="J18" s="82"/>
-      <c r="K18" s="95"/>
+      <c r="K18" s="94"/>
       <c r="L18" s="82"/>
-      <c r="M18" s="95"/>
-      <c r="N18" s="79"/>
+      <c r="M18" s="94"/>
+      <c r="N18" s="79" t="s">
+        <v>2</v>
+      </c>
       <c r="O18" s="85"/>
-      <c r="P18" s="95"/>
+      <c r="P18" s="94"/>
       <c r="Q18" s="86" t="s">
         <v>110</v>
       </c>
@@ -4746,7 +4698,9 @@
       <c r="K19" s="79"/>
       <c r="L19" s="84"/>
       <c r="M19" s="79"/>
-      <c r="N19" s="79"/>
+      <c r="N19" s="79" t="s">
+        <v>2</v>
+      </c>
       <c r="O19" s="85"/>
       <c r="P19" s="79"/>
       <c r="Q19" s="86" t="s">
@@ -5210,7 +5164,9 @@
       <c r="K20" s="79"/>
       <c r="L20" s="84"/>
       <c r="M20" s="79"/>
-      <c r="N20" s="79"/>
+      <c r="N20" s="79" t="s">
+        <v>2</v>
+      </c>
       <c r="O20" s="85"/>
       <c r="P20" s="79"/>
       <c r="Q20" s="86" t="s">
@@ -5674,7 +5630,9 @@
       <c r="K21" s="79"/>
       <c r="L21" s="84"/>
       <c r="M21" s="79"/>
-      <c r="N21" s="79"/>
+      <c r="N21" s="79" t="s">
+        <v>2</v>
+      </c>
       <c r="O21" s="85"/>
       <c r="P21" s="79"/>
       <c r="Q21" s="86" t="s">
@@ -6115,21 +6073,11 @@
       <c r="C22" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="82" t="n">
-        <v>8.35416666666667</v>
-      </c>
-      <c r="E22" s="79" t="n">
-        <v>46136</v>
-      </c>
-      <c r="F22" s="82" t="n">
-        <v>8.8125</v>
-      </c>
-      <c r="G22" s="82" t="n">
-        <v>8.35416666666667</v>
-      </c>
-      <c r="H22" s="82" t="n">
-        <v>8.8125</v>
-      </c>
+      <c r="D22" s="82"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
       <c r="I22" s="83" t="n">
         <f aca="false">IFERROR(IF(N22="Strict",IF(C22="Normal",IFERROR(IF((HOUR(IF(AQ22&lt;=AR22,BB22-AR22,BB22-AQ22))+MINUTE(IF(AQ22&lt;=AR22,BB22-AR22,BB22-AQ22))/60)&gt;=6,HOUR(IF(AQ22&lt;=AR22,BB22-AR22,BB22-AQ22))+MINUTE(IF(AQ22&lt;=AR22,BB22-AR22,BB22-AQ22))/60-1,HOUR(IF(AQ22&lt;=AR22,BB22-AR22,BB22-AQ22))+MINUTE(IF(AQ22&lt;=AR22,BB22-AR22,BB22-AQ22))/60),0),0),IF(N22="Flexi",IF(C22="Normal",IF((HOUR(BB22-AR22)+MINUTE(BB22-AR22)/60)&gt;=6,(HOUR(BB22-AR22)+MINUTE(BB22-AR22)/60)-1,(HOUR(BB22-AR22)+MINUTE(BB22-AR22)/60)),0),0)),0)</f>
         <v>0</v>
@@ -6141,7 +6089,7 @@
       <c r="N22" s="79"/>
       <c r="O22" s="85"/>
       <c r="P22" s="79"/>
-      <c r="Q22" s="94"/>
+      <c r="Q22" s="86"/>
       <c r="R22" s="87" t="n">
         <f aca="false">IF(AND(C22="Normal",I22&gt;0),(8-S22),0)-IF(AND(C22="Normal",OR(C23="Special Holiday",C23="Working - Legal Holiday on RD",C23="Working - Special Holiday on RD",C23="Legal Holiday",C23="Legal Holiday on RD",C23="Special Holiday on RD")),BN22,0)+IF(AND(OR(C22="Normal",C22="Leave",C22="Rest Day"),OR(C21="Special Holiday",C21="Working - Legal Holiday on RD",C21="Working - Special Holiday on RD",C21="Legal Holiday")),BN21,0)</f>
         <v>0</v>
@@ -6244,19 +6192,19 @@
       </c>
       <c r="AQ22" s="89" t="str">
         <f aca="false">TEXT(D22,"HH:MM")&amp;" "&amp;TEXT(A22,"DD-mmm-YY")</f>
-        <v>08:30 24-Apr-26</v>
+        <v>00:00 24-Apr-26</v>
       </c>
       <c r="AR22" s="89" t="str">
         <f aca="false">TEXT(G22,"HH:MM")&amp;" "&amp;TEXT(A22,"DD-mmm-YY")</f>
-        <v>08:30 24-Apr-26</v>
+        <v>00:00 24-Apr-26</v>
       </c>
       <c r="AS22" s="60" t="str">
         <f aca="false">IF($AR$1&lt;D22,AR22,IF(AT22&lt;=AR22,AR22,AT22))</f>
-        <v>08:30 24-Apr-26</v>
+        <v>22:00 23-Apr-26</v>
       </c>
       <c r="AT22" s="60" t="str">
         <f aca="false">IF(AND(D22&gt;=0,D22&lt;0.25),TEXT($AR$1,"HH:MM")&amp;" "&amp;TEXT((A22-1),"dd-mmm-yy"),TEXT($AR$1,"HH:MM")&amp;" "&amp;TEXT(A22,"dd-mmm-yy"))</f>
-        <v>22:00 24-Apr-26</v>
+        <v>22:00 23-Apr-26</v>
       </c>
       <c r="AU22" s="40" t="e">
         <f aca="false" t="array" ref="AU22:AU22">MAX(AQ22:AS22+0)</f>
@@ -6280,7 +6228,7 @@
       </c>
       <c r="AZ22" s="60" t="str">
         <f aca="false">IF(AND(D22&gt;=0,D22&lt;0.25,L22&lt;0.916666666666667,A22&gt;M22),TEXT($AR$2,"HH:MM")&amp;" "&amp;TEXT(A22,"DD-mmm-YY"),TEXT($AR$2,"HH:MM")&amp;" "&amp;TEXT((A22+1),"DD-mmm-YY"))</f>
-        <v>06:00 25-Apr-26</v>
+        <v>06:00 24-Apr-26</v>
       </c>
       <c r="BA22" s="40" t="e">
         <f aca="false" t="array" ref="BA22:BA22">MIN(AY22:AZ22+0)</f>
@@ -6288,11 +6236,11 @@
       </c>
       <c r="BB22" s="60" t="str">
         <f aca="false">IF(G22&gt;H22,TEXT(H22,"HH:MM")&amp;" "&amp;TEXT(E22,"DD-mmm-YY"),IF(H22&gt;1,TEXT(H22,"HH:MM")&amp;" "&amp;TEXT(E22,"DD-mmm-YY"),TEXT(H22,"HH:MM")&amp;" "&amp;TEXT(A22,"DD-mmm-YY")))</f>
-        <v>19:30 24-Apr-26</v>
+        <v>00:00 24-Apr-26</v>
       </c>
       <c r="BC22" s="60" t="str">
         <f aca="false">IF(N22="Flexi",TEXT(G22+$BC$1,"HH:MM")&amp;" "&amp;TEXT(E22,"DD-mmm-YY"),TEXT(F22,"HH:MM")&amp;" "&amp;TEXT(E22,"DD-mmm-YY"))</f>
-        <v>19:30 24-Apr-26</v>
+        <v>00:00 30-Dec-99</v>
       </c>
       <c r="BD22" s="90" t="e">
         <f aca="false" t="array" ref="BD22:BD22">MIN(BB22:BC22+0)</f>
@@ -6300,7 +6248,7 @@
       </c>
       <c r="BE22" s="60" t="str">
         <f aca="false">IF(D22&gt;0.25,TEXT($AR$2,"HH:MM")&amp;" "&amp;TEXT(IF(BG22&lt;H22,A22+1,E22),"DD-mmm-YY"),IF(D22&gt;=0,TEXT($AR$2,"HH:MM")&amp;" "&amp;TEXT(IF(BG22&lt;H22,A22+1,E22)-1,"DD-mmm-YY"),TEXT($AR$2,"HH:MM")&amp;" "&amp;TEXT(IF(BG22&lt;H22,A22+1,E22),"DD-mmm-YY")))</f>
-        <v>06:00 25-Apr-26</v>
+        <v>06:00 29-Dec-99</v>
       </c>
       <c r="BF22" s="40" t="e">
         <f aca="false" t="array" ref="BF22:BF22">IF(N22="Flexi",IF(AND(BB22&gt;BC22,BB22&lt;BE22),BB22,MIN(BB22:BE22+0)),MIN(BB22:BE22+0))</f>
@@ -6593,7 +6541,7 @@
       <c r="N23" s="79"/>
       <c r="O23" s="85"/>
       <c r="P23" s="79"/>
-      <c r="Q23" s="94"/>
+      <c r="Q23" s="86"/>
       <c r="R23" s="87" t="n">
         <f aca="false">IF(AND(C23="Normal",I23&gt;0),(8-S23),0)-IF(AND(C23="Normal",OR(C24="Special Holiday",C24="Working - Legal Holiday on RD",C24="Working - Special Holiday on RD",C24="Legal Holiday",C24="Legal Holiday on RD",C24="Special Holiday on RD")),BN23,0)+IF(AND(OR(C23="Normal",C23="Leave",C23="Rest Day"),OR(C22="Special Holiday",C22="Working - Legal Holiday on RD",C22="Working - Special Holiday on RD",C22="Legal Holiday")),BN22,0)</f>
         <v>0</v>
@@ -7045,7 +6993,7 @@
       <c r="N24" s="79"/>
       <c r="O24" s="85"/>
       <c r="P24" s="79"/>
-      <c r="Q24" s="94"/>
+      <c r="Q24" s="86"/>
       <c r="R24" s="87" t="n">
         <f aca="false">IF(AND(C24="Normal",I24&gt;0),(8-S24),0)-IF(AND(C24="Normal",OR(C25="Special Holiday",C25="Working - Legal Holiday on RD",C25="Working - Special Holiday on RD",C25="Legal Holiday",C25="Legal Holiday on RD",C25="Special Holiday on RD")),BN24,0)+IF(AND(OR(C24="Normal",C24="Leave",C24="Rest Day"),OR(C23="Special Holiday",C23="Working - Legal Holiday on RD",C23="Working - Special Holiday on RD",C23="Legal Holiday")),BN23,0)</f>
         <v>0</v>
@@ -7500,11 +7448,13 @@
         <f aca="false">IFERROR(IF(N25="Strict",IF(C25="Normal",IFERROR(IF((HOUR(IF(AQ25&lt;=AR25,BB25-AR25,BB25-AQ25))+MINUTE(IF(AQ25&lt;=AR25,BB25-AR25,BB25-AQ25))/60)&gt;=6,HOUR(IF(AQ25&lt;=AR25,BB25-AR25,BB25-AQ25))+MINUTE(IF(AQ25&lt;=AR25,BB25-AR25,BB25-AQ25))/60-1,HOUR(IF(AQ25&lt;=AR25,BB25-AR25,BB25-AQ25))+MINUTE(IF(AQ25&lt;=AR25,BB25-AR25,BB25-AQ25))/60),0),0),IF(N25="Flexi",IF(C25="Normal",IF((HOUR(BB25-AR25)+MINUTE(BB25-AR25)/60)&gt;=6,(HOUR(BB25-AR25)+MINUTE(BB25-AR25)/60)-1,(HOUR(BB25-AR25)+MINUTE(BB25-AR25)/60)),0),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="96"/>
+      <c r="J25" s="95"/>
       <c r="K25" s="79"/>
       <c r="L25" s="82"/>
       <c r="M25" s="79"/>
-      <c r="N25" s="79"/>
+      <c r="N25" s="79" t="s">
+        <v>2</v>
+      </c>
       <c r="O25" s="85"/>
       <c r="P25" s="79"/>
       <c r="Q25" s="86" t="s">
@@ -7964,11 +7914,13 @@
         <f aca="false">IFERROR(IF(N26="Strict",IF(C26="Normal",IFERROR(IF((HOUR(IF(AQ26&lt;=AR26,BB26-AR26,BB26-AQ26))+MINUTE(IF(AQ26&lt;=AR26,BB26-AR26,BB26-AQ26))/60)&gt;=6,HOUR(IF(AQ26&lt;=AR26,BB26-AR26,BB26-AQ26))+MINUTE(IF(AQ26&lt;=AR26,BB26-AR26,BB26-AQ26))/60-1,HOUR(IF(AQ26&lt;=AR26,BB26-AR26,BB26-AQ26))+MINUTE(IF(AQ26&lt;=AR26,BB26-AR26,BB26-AQ26))/60),0),0),IF(N26="Flexi",IF(C26="Normal",IF((HOUR(BB26-AR26)+MINUTE(BB26-AR26)/60)&gt;=6,(HOUR(BB26-AR26)+MINUTE(BB26-AR26)/60)-1,(HOUR(BB26-AR26)+MINUTE(BB26-AR26)/60)),0),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="96"/>
+      <c r="J26" s="95"/>
       <c r="K26" s="79"/>
       <c r="L26" s="82"/>
       <c r="M26" s="79"/>
-      <c r="N26" s="79"/>
+      <c r="N26" s="79" t="s">
+        <v>2</v>
+      </c>
       <c r="O26" s="85"/>
       <c r="P26" s="79"/>
       <c r="Q26" s="86" t="s">
@@ -8432,7 +8384,9 @@
       <c r="K27" s="79"/>
       <c r="L27" s="84"/>
       <c r="M27" s="79"/>
-      <c r="N27" s="79"/>
+      <c r="N27" s="79" t="s">
+        <v>2</v>
+      </c>
       <c r="O27" s="85"/>
       <c r="P27" s="79"/>
       <c r="Q27" s="86" t="s">
@@ -8896,7 +8850,9 @@
       <c r="K28" s="79"/>
       <c r="L28" s="84"/>
       <c r="M28" s="79"/>
-      <c r="N28" s="79"/>
+      <c r="N28" s="79" t="s">
+        <v>2</v>
+      </c>
       <c r="O28" s="85"/>
       <c r="P28" s="79"/>
       <c r="Q28" s="86" t="s">
@@ -9351,7 +9307,7 @@
       <c r="N29" s="79"/>
       <c r="O29" s="85"/>
       <c r="P29" s="79"/>
-      <c r="Q29" s="97"/>
+      <c r="Q29" s="96"/>
       <c r="R29" s="87" t="n">
         <f aca="false">IF(AND(C29="Normal",I29&gt;0),(8-S29),0)-IF(AND(C29="Normal",OR(C30="Special Holiday",C30="Working - Legal Holiday on RD",C30="Working - Special Holiday on RD",C30="Legal Holiday",C30="Legal Holiday on RD",C30="Special Holiday on RD")),BN29,0)+IF(AND(OR(C29="Normal",C29="Leave",C29="Rest Day"),OR(C28="Special Holiday",C28="Working - Legal Holiday on RD",C28="Working - Special Holiday on RD",C28="Legal Holiday")),BN28,0)</f>
         <v>0</v>
@@ -9801,7 +9757,7 @@
       <c r="N30" s="79"/>
       <c r="O30" s="85"/>
       <c r="P30" s="79"/>
-      <c r="Q30" s="98"/>
+      <c r="Q30" s="97"/>
       <c r="R30" s="87" t="n">
         <f aca="false">IF(AND(C30="Normal",I30&gt;0),(8-S30),0)-IF(AND(C30="Normal",OR(C31="Special Holiday",C31="Working - Legal Holiday on RD",C31="Working - Special Holiday on RD",C31="Legal Holiday",C31="Legal Holiday on RD",C31="Special Holiday on RD")),BN30,0)+IF(AND(OR(C30="Normal",C30="Leave",C30="Rest Day"),OR(C29="Special Holiday",C29="Working - Legal Holiday on RD",C29="Working - Special Holiday on RD",C29="Legal Holiday")),BN29,0)</f>
         <v>0</v>
@@ -10230,357 +10186,357 @@
       <c r="BY31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J32" s="99" t="s">
+      <c r="J32" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="K32" s="99"/>
-      <c r="L32" s="99"/>
-      <c r="M32" s="99"/>
-      <c r="N32" s="100"/>
-      <c r="O32" s="100"/>
-      <c r="P32" s="100"/>
-      <c r="R32" s="101" t="n">
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="98"/>
+      <c r="N32" s="99"/>
+      <c r="O32" s="99"/>
+      <c r="P32" s="99"/>
+      <c r="R32" s="100" t="n">
         <f aca="false">SUM(R14:R31)</f>
         <v>0</v>
       </c>
-      <c r="S32" s="101" t="n">
+      <c r="S32" s="100" t="n">
         <f aca="false">SUM(S14:S31)</f>
         <v>0</v>
       </c>
-      <c r="T32" s="101" t="n">
+      <c r="T32" s="100" t="n">
         <f aca="false">SUM(T14:T31)</f>
         <v>0</v>
       </c>
-      <c r="U32" s="101" t="n">
+      <c r="U32" s="100" t="n">
         <f aca="false">SUM(U14:U31)</f>
         <v>0</v>
       </c>
-      <c r="V32" s="101" t="n">
+      <c r="V32" s="100" t="n">
         <f aca="false">SUM(V14:V31)</f>
         <v>0</v>
       </c>
-      <c r="W32" s="101" t="n">
+      <c r="W32" s="100" t="n">
         <f aca="false">SUM(W14:W31)</f>
         <v>0</v>
       </c>
-      <c r="X32" s="101" t="n">
+      <c r="X32" s="100" t="n">
         <f aca="false">SUM(X14:X31)</f>
         <v>0</v>
       </c>
-      <c r="Y32" s="101" t="n">
+      <c r="Y32" s="100" t="n">
         <f aca="false">SUM(Y14:Y31)</f>
         <v>0</v>
       </c>
-      <c r="Z32" s="101" t="n">
+      <c r="Z32" s="100" t="n">
         <f aca="false">SUM(Z14:Z31)</f>
         <v>0</v>
       </c>
-      <c r="AA32" s="101" t="n">
+      <c r="AA32" s="100" t="n">
         <f aca="false">SUM(AA14:AA31)</f>
         <v>0</v>
       </c>
-      <c r="AB32" s="101" t="n">
+      <c r="AB32" s="100" t="n">
         <f aca="false">SUM(AB14:AB31)</f>
         <v>0</v>
       </c>
-      <c r="AC32" s="101" t="n">
+      <c r="AC32" s="100" t="n">
         <f aca="false">SUM(AC14:AC31)</f>
         <v>0</v>
       </c>
-      <c r="AD32" s="101" t="n">
+      <c r="AD32" s="100" t="n">
         <f aca="false">SUM(AD14:AD31)</f>
         <v>0</v>
       </c>
-      <c r="AE32" s="101" t="n">
+      <c r="AE32" s="100" t="n">
         <f aca="false">SUM(AE14:AE31)</f>
         <v>0</v>
       </c>
-      <c r="AF32" s="101" t="n">
+      <c r="AF32" s="100" t="n">
         <f aca="false">SUM(AF14:AF31)</f>
         <v>0</v>
       </c>
-      <c r="AG32" s="101" t="n">
+      <c r="AG32" s="100" t="n">
         <f aca="false">SUM(AG14:AG31)</f>
         <v>0</v>
       </c>
-      <c r="AH32" s="101" t="n">
+      <c r="AH32" s="100" t="n">
         <f aca="false">SUM(AH14:AH31)</f>
         <v>0</v>
       </c>
-      <c r="AI32" s="101" t="n">
+      <c r="AI32" s="100" t="n">
         <f aca="false">SUM(AI14:AI31)</f>
         <v>0</v>
       </c>
-      <c r="AJ32" s="101" t="n">
+      <c r="AJ32" s="100" t="n">
         <f aca="false">SUM(AJ14:AJ31)</f>
         <v>0</v>
       </c>
-      <c r="AK32" s="101" t="n">
+      <c r="AK32" s="100" t="n">
         <f aca="false">SUM(AK14:AK31)</f>
         <v>0</v>
       </c>
-      <c r="AL32" s="101" t="n">
+      <c r="AL32" s="100" t="n">
         <f aca="false">SUM(AL14:AL31)</f>
         <v>0</v>
       </c>
-      <c r="AM32" s="101" t="n">
+      <c r="AM32" s="100" t="n">
         <f aca="false">SUM(AM14:AM31)</f>
         <v>0</v>
       </c>
-      <c r="AN32" s="101" t="n">
+      <c r="AN32" s="100" t="n">
         <f aca="false">SUM(AN14:AN31)</f>
         <v>0</v>
       </c>
-      <c r="AO32" s="101" t="n">
+      <c r="AO32" s="100" t="n">
         <f aca="false">SUM(AO14:AO31)</f>
         <v>0</v>
       </c>
-      <c r="AP32" s="101" t="n">
+      <c r="AP32" s="100" t="n">
         <f aca="false">SUM(AP14:AP31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M33" s="100"/>
-      <c r="N33" s="100"/>
-      <c r="O33" s="100"/>
-      <c r="P33" s="100"/>
-      <c r="R33" s="102"/>
-      <c r="S33" s="102"/>
-      <c r="T33" s="102"/>
-      <c r="U33" s="102"/>
-      <c r="V33" s="102"/>
-      <c r="W33" s="102"/>
-      <c r="X33" s="102"/>
-      <c r="Y33" s="102"/>
-      <c r="Z33" s="102"/>
-      <c r="AA33" s="102"/>
-      <c r="AB33" s="102"/>
-      <c r="AC33" s="102"/>
-      <c r="AD33" s="102"/>
-      <c r="AE33" s="102"/>
-      <c r="AF33" s="102"/>
-      <c r="AG33" s="102"/>
-      <c r="AH33" s="102"/>
-      <c r="AI33" s="102"/>
-      <c r="AJ33" s="102"/>
-      <c r="AK33" s="102"/>
-      <c r="AL33" s="102"/>
-      <c r="AM33" s="102"/>
-      <c r="AN33" s="102"/>
-      <c r="AO33" s="102"/>
-      <c r="AP33" s="102"/>
+      <c r="M33" s="99"/>
+      <c r="N33" s="99"/>
+      <c r="O33" s="99"/>
+      <c r="P33" s="99"/>
+      <c r="R33" s="101"/>
+      <c r="S33" s="101"/>
+      <c r="T33" s="101"/>
+      <c r="U33" s="101"/>
+      <c r="V33" s="101"/>
+      <c r="W33" s="101"/>
+      <c r="X33" s="101"/>
+      <c r="Y33" s="101"/>
+      <c r="Z33" s="101"/>
+      <c r="AA33" s="101"/>
+      <c r="AB33" s="101"/>
+      <c r="AC33" s="101"/>
+      <c r="AD33" s="101"/>
+      <c r="AE33" s="101"/>
+      <c r="AF33" s="101"/>
+      <c r="AG33" s="101"/>
+      <c r="AH33" s="101"/>
+      <c r="AI33" s="101"/>
+      <c r="AJ33" s="101"/>
+      <c r="AK33" s="101"/>
+      <c r="AL33" s="101"/>
+      <c r="AM33" s="101"/>
+      <c r="AN33" s="101"/>
+      <c r="AO33" s="101"/>
+      <c r="AP33" s="101"/>
     </row>
     <row r="34" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="103" t="s">
+      <c r="A34" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="104" t="s">
+      <c r="C34" s="103" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="104"/>
-      <c r="E34" s="104"/>
-      <c r="H34" s="103" t="s">
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="H34" s="102" t="s">
         <v>114</v>
       </c>
       <c r="I34" s="2"/>
-      <c r="K34" s="104" t="s">
+      <c r="K34" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="L34" s="104"/>
-      <c r="M34" s="104"/>
-      <c r="N34" s="105"/>
+      <c r="L34" s="103"/>
+      <c r="M34" s="103"/>
+      <c r="N34" s="104"/>
     </row>
     <row r="35" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="103"/>
-      <c r="C35" s="106"/>
-      <c r="D35" s="106"/>
-      <c r="E35" s="106"/>
+      <c r="A35" s="102"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="105"/>
     </row>
     <row r="37" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="107" t="s">
+      <c r="A37" s="106" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="108" t="s">
+      <c r="B37" s="107" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="108" t="s">
+      <c r="C37" s="107" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="108" t="s">
+      <c r="D37" s="107" t="s">
         <v>101</v>
       </c>
-      <c r="E37" s="108" t="s">
+      <c r="E37" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="F37" s="108" t="s">
+      <c r="F37" s="107" t="s">
         <v>56</v>
       </c>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" s="111" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="109" t="s">
+    <row r="38" s="110" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="108" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="110" t="n">
+      <c r="B38" s="109" t="n">
         <f aca="false">R32+S32</f>
         <v>0</v>
       </c>
-      <c r="C38" s="110" t="n">
+      <c r="C38" s="109" t="n">
         <f aca="false">AK32</f>
         <v>0</v>
       </c>
-      <c r="D38" s="110" t="n">
+      <c r="D38" s="109" t="n">
         <f aca="false">Y32</f>
         <v>0</v>
       </c>
-      <c r="E38" s="110" t="n">
+      <c r="E38" s="109" t="n">
         <f aca="false">AE32</f>
         <v>0</v>
       </c>
-      <c r="F38" s="110" t="n">
+      <c r="F38" s="109" t="n">
         <f aca="false">S32</f>
         <v>0</v>
       </c>
-      <c r="I38" s="112"/>
+      <c r="I38" s="111"/>
     </row>
-    <row r="39" s="111" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="109" t="s">
+    <row r="39" s="110" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="B39" s="110" t="n">
+      <c r="B39" s="109" t="n">
         <f aca="false">T32</f>
         <v>0</v>
       </c>
-      <c r="C39" s="110" t="n">
+      <c r="C39" s="109" t="n">
         <f aca="false">AL32</f>
         <v>0</v>
       </c>
-      <c r="D39" s="110" t="n">
+      <c r="D39" s="109" t="n">
         <f aca="false">Z32</f>
         <v>0</v>
       </c>
-      <c r="E39" s="110" t="n">
+      <c r="E39" s="109" t="n">
         <f aca="false">AF32</f>
         <v>0</v>
       </c>
-      <c r="F39" s="113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="112"/>
+      <c r="F39" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="111"/>
     </row>
-    <row r="40" s="111" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="109" t="s">
+    <row r="40" s="110" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="B40" s="110" t="n">
+      <c r="B40" s="109" t="n">
         <f aca="false">U32</f>
         <v>0</v>
       </c>
-      <c r="C40" s="110" t="n">
+      <c r="C40" s="109" t="n">
         <f aca="false">AM32</f>
         <v>0</v>
       </c>
-      <c r="D40" s="110" t="n">
+      <c r="D40" s="109" t="n">
         <f aca="false">AA32</f>
         <v>0</v>
       </c>
-      <c r="E40" s="110" t="n">
+      <c r="E40" s="109" t="n">
         <f aca="false">AG32</f>
         <v>0</v>
       </c>
-      <c r="F40" s="113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="112"/>
+      <c r="F40" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="111"/>
     </row>
-    <row r="41" s="111" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="109" t="s">
+    <row r="41" s="110" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="110" t="n">
+      <c r="B41" s="109" t="n">
         <f aca="false">V32</f>
         <v>0</v>
       </c>
-      <c r="C41" s="110" t="n">
+      <c r="C41" s="109" t="n">
         <f aca="false">AN32</f>
         <v>0</v>
       </c>
-      <c r="D41" s="110" t="n">
+      <c r="D41" s="109" t="n">
         <f aca="false">AB32</f>
         <v>0</v>
       </c>
-      <c r="E41" s="110" t="n">
+      <c r="E41" s="109" t="n">
         <f aca="false">AH32</f>
         <v>0</v>
       </c>
-      <c r="F41" s="113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="112"/>
+      <c r="F41" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="111"/>
     </row>
-    <row r="42" s="111" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="109" t="s">
+    <row r="42" s="110" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="108" t="s">
         <v>117</v>
       </c>
-      <c r="B42" s="110" t="n">
+      <c r="B42" s="109" t="n">
         <f aca="false">W32</f>
         <v>0</v>
       </c>
-      <c r="C42" s="110" t="n">
+      <c r="C42" s="109" t="n">
         <f aca="false">AO32</f>
         <v>0</v>
       </c>
-      <c r="D42" s="110" t="n">
+      <c r="D42" s="109" t="n">
         <f aca="false">AC32</f>
         <v>0</v>
       </c>
-      <c r="E42" s="110" t="n">
+      <c r="E42" s="109" t="n">
         <f aca="false">AI32</f>
         <v>0</v>
       </c>
-      <c r="F42" s="113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="112"/>
+      <c r="F42" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="111"/>
     </row>
-    <row r="43" s="111" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="109" t="s">
+    <row r="43" s="110" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="108" t="s">
         <v>118</v>
       </c>
-      <c r="B43" s="110" t="n">
+      <c r="B43" s="109" t="n">
         <f aca="false">X32</f>
         <v>0</v>
       </c>
-      <c r="C43" s="110" t="n">
+      <c r="C43" s="109" t="n">
         <f aca="false">AP32</f>
         <v>0</v>
       </c>
-      <c r="D43" s="110" t="n">
+      <c r="D43" s="109" t="n">
         <f aca="false">AD32</f>
         <v>0</v>
       </c>
-      <c r="E43" s="110" t="n">
+      <c r="E43" s="109" t="n">
         <f aca="false">AJ32</f>
         <v>0</v>
       </c>
-      <c r="F43" s="113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="112"/>
+      <c r="F43" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="111"/>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="114" t="s">
+      <c r="A44" s="113" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="115" t="str">
+      <c r="B44" s="114" t="str">
         <f aca="false">COUNTIF(C14:C29,"Leave")&amp;" "&amp;"Leaves"&amp;" "&amp;"-"&amp;IF(C14="Leave",(TEXT(A14,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C15="Leave",(TEXT(A15,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C16="Leave",(TEXT(A16,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C17="Leave",(TEXT(A17,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C18="Leave",(TEXT(A18,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C19="Leave",(TEXT(A19,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C20="Leave",(TEXT(A20,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C21="Leave",(TEXT(A21,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C22="Leave",(TEXT(A22,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C23="Leave",(TEXT(A23,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C24="Leave",(TEXT(A24,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C25="Leave",(TEXT(A25,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C26="Leave",(TEXT(A26,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C27="Leave",(TEXT(A27,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C28="Leave",(TEXT(A28,"DD-mmm")&amp;","),"")&amp;" "&amp;IF(C29="Leave",(TEXT(A29,"DD-mmm")&amp;","),"")</f>
         <v>0 Leaves -               </v>
       </c>
-      <c r="C44" s="115"/>
-      <c r="D44" s="115"/>
-      <c r="E44" s="115"/>
-      <c r="F44" s="115"/>
+      <c r="C44" s="114"/>
+      <c r="D44" s="114"/>
+      <c r="E44" s="114"/>
+      <c r="F44" s="114"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="d9ff" formatCells="false" formatColumns="false" formatRows="false" autoFilter="false" pivotTables="false"/>
@@ -10627,10 +10583,10 @@
     <mergeCell ref="B44:F44"/>
   </mergeCells>
   <conditionalFormatting sqref="B14:B30">
-    <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Sun" dxfId="6">
+    <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Sun" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("Sun",B14)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="3" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Sat" dxfId="7">
+    <cfRule type="containsText" priority="3" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Sat" dxfId="1">
       <formula>NOT(ISERROR(SEARCH("Sat",B14)))</formula>
     </cfRule>
   </conditionalFormatting>
